--- a/web/public/forms/orig/o-sajindaeji.xlsx
+++ b/web/public/forms/orig/o-sajindaeji.xlsx
@@ -550,7 +550,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -3687,7 +3687,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">

--- a/web/public/forms/orig/o-sajindaeji.xlsx
+++ b/web/public/forms/orig/o-sajindaeji.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사진대지" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-사진대지" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'사진대지'!$A$1:$F$351</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'예시-사진대지'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -132,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -167,9 +165,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -848,10 +843,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F35" s="10">
-        <f>IF(N(F19)=0,"",F19)</f>
-        <v/>
-      </c>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36" ht="8" customHeight="1"/>
     <row r="37" ht="34" customHeight="1">
@@ -867,10 +859,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B38" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B38" s="11" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="n"/>
@@ -1146,10 +1135,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F70" s="10">
-        <f>IF(N(F54)=0,"",F54)</f>
-        <v/>
-      </c>
+      <c r="F70" s="10" t="n"/>
     </row>
     <row r="71" ht="8" customHeight="1"/>
     <row r="72" ht="34" customHeight="1">
@@ -1165,10 +1151,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B73" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B73" s="11" t="n"/>
       <c r="C73" s="6" t="n"/>
       <c r="D73" s="6" t="n"/>
       <c r="E73" s="6" t="n"/>
@@ -1444,10 +1427,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F105" s="10">
-        <f>IF(N(F89)=0,"",F89)</f>
-        <v/>
-      </c>
+      <c r="F105" s="10" t="n"/>
     </row>
     <row r="106" ht="8" customHeight="1"/>
     <row r="107" ht="34" customHeight="1">
@@ -1463,10 +1443,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B108" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B108" s="11" t="n"/>
       <c r="C108" s="6" t="n"/>
       <c r="D108" s="6" t="n"/>
       <c r="E108" s="6" t="n"/>
@@ -1742,10 +1719,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F140" s="10">
-        <f>IF(N(F124)=0,"",F124)</f>
-        <v/>
-      </c>
+      <c r="F140" s="10" t="n"/>
     </row>
     <row r="141" ht="8" customHeight="1"/>
     <row r="142" ht="34" customHeight="1">
@@ -1761,10 +1735,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B143" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B143" s="11" t="n"/>
       <c r="C143" s="6" t="n"/>
       <c r="D143" s="6" t="n"/>
       <c r="E143" s="6" t="n"/>
@@ -2040,10 +2011,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F175" s="10">
-        <f>IF(N(F159)=0,"",F159)</f>
-        <v/>
-      </c>
+      <c r="F175" s="10" t="n"/>
     </row>
     <row r="176" ht="8" customHeight="1"/>
     <row r="177" ht="34" customHeight="1">
@@ -2059,10 +2027,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B178" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B178" s="11" t="n"/>
       <c r="C178" s="6" t="n"/>
       <c r="D178" s="6" t="n"/>
       <c r="E178" s="6" t="n"/>
@@ -2338,10 +2303,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F210" s="10">
-        <f>IF(N(F194)=0,"",F194)</f>
-        <v/>
-      </c>
+      <c r="F210" s="10" t="n"/>
     </row>
     <row r="211" ht="8" customHeight="1"/>
     <row r="212" ht="34" customHeight="1">
@@ -2357,10 +2319,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B213" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B213" s="11" t="n"/>
       <c r="C213" s="6" t="n"/>
       <c r="D213" s="6" t="n"/>
       <c r="E213" s="6" t="n"/>
@@ -2636,10 +2595,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F245" s="10">
-        <f>IF(N(F229)=0,"",F229)</f>
-        <v/>
-      </c>
+      <c r="F245" s="10" t="n"/>
     </row>
     <row r="246" ht="8" customHeight="1"/>
     <row r="247" ht="34" customHeight="1">
@@ -2655,10 +2611,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B248" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B248" s="11" t="n"/>
       <c r="C248" s="6" t="n"/>
       <c r="D248" s="6" t="n"/>
       <c r="E248" s="6" t="n"/>
@@ -2934,10 +2887,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F280" s="10">
-        <f>IF(N(F264)=0,"",F264)</f>
-        <v/>
-      </c>
+      <c r="F280" s="10" t="n"/>
     </row>
     <row r="281" ht="8" customHeight="1"/>
     <row r="282" ht="34" customHeight="1">
@@ -2953,10 +2903,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B283" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B283" s="11" t="n"/>
       <c r="C283" s="6" t="n"/>
       <c r="D283" s="6" t="n"/>
       <c r="E283" s="6" t="n"/>
@@ -3232,10 +3179,7 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F315" s="10">
-        <f>IF(N(F299)=0,"",F299)</f>
-        <v/>
-      </c>
+      <c r="F315" s="10" t="n"/>
     </row>
     <row r="316" ht="8" customHeight="1"/>
     <row r="317" ht="34" customHeight="1">
@@ -3251,10 +3195,7 @@
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="B318" s="11">
-        <f>IF(B3="","",B3)</f>
-        <v/>
-      </c>
+      <c r="B318" s="11" t="n"/>
       <c r="C318" s="6" t="n"/>
       <c r="D318" s="6" t="n"/>
       <c r="E318" s="6" t="n"/>
@@ -3530,12 +3471,10 @@
           <t>일  자</t>
         </is>
       </c>
-      <c r="F350" s="10">
-        <f>IF(N(F334)=0,"",F334)</f>
-        <v/>
-      </c>
+      <c r="F350" s="10" t="n"/>
     </row>
     <row r="351" ht="8" customHeight="1"/>
+    <row r="352"/>
     <row r="353" ht="48.5" customHeight="1">
       <c r="A353" s="12" t="inlineStr">
         <is>
@@ -3664,380 +3603,4 @@
     <brk id="316" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>사  진  대  지</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>사진 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>(사진)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>내  용</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>가시설(흙막이판) 설치</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>위  치</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>STA.0+120 ~ 0+160</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>일  자</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>46154</v>
-      </c>
-    </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>사진 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>(사진)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>내  용</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>PC 암거 거치</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>위  치</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>STA.0+140</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>일  자</t>
-        </is>
-      </c>
-      <c r="F35" s="10">
-        <f>IF(N(F19)=0,"",F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="8" customHeight="1"/>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A6:F17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A22:F33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B18:F18"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/orig/o-sajindaeji.xlsx
+++ b/web/public/forms/orig/o-sajindaeji.xlsx
@@ -545,7 +545,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
